--- a/internal_doc/05.测试设计/story/selector/Story-selector测试用例.xlsx
+++ b/internal_doc/05.测试设计/story/selector/Story-selector测试用例.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="376" uniqueCount="239">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="470" uniqueCount="320">
   <si>
     <t>name</t>
   </si>
@@ -1070,10 +1070,6 @@
 2、查询结果不影响原始数据，即find后原始数据不变</t>
   </si>
   <si>
-    <t>1、进入sdb，find({},{&lt;fieldName&gt;:{&lt;$substr:[value1,value2]&gt;}})查询数组内满足条件的子串，指定的value1/value2非整数
-2、检查查询结果</t>
-  </si>
-  <si>
     <t>1、进入sdb，find({},{&lt;fieldName&gt;:{&lt;$substr:[value1,value2]&gt;}})查询数组内满足条件的子串，指定的目标字段不存在
 2、检查查询结果</t>
   </si>
@@ -1100,10 +1096,369 @@
     <t>$substr，指定从第n个子串开始取值(n&gt;0)，目标数组为空</t>
   </si>
   <si>
-    <t>$substr，指定的value1/value2非整数</t>
-  </si>
-  <si>
     <t>$substr，指定的目标字段不存在</t>
+  </si>
+  <si>
+    <t>$substr，指定的value1/value2非字符串</t>
+  </si>
+  <si>
+    <t>1、进入sdb，find({},{&lt;fieldName&gt;:{&lt;$substr:[value1,value2]&gt;}})查询数组内满足条件的子串，指定的value1/value2非字符串
+2、检查查询结果</t>
+  </si>
+  <si>
+    <t>功能说明：返回字符串长度，不包括终止符。非字符串返回 null。
+格式：find({},{&lt;fieldname&gt;:{&lt;$strlen:1&gt;}})，{$strlen:1}中1没有特殊含义，仅作为占位符出现</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>$strlen，目标字符串长度为0</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>$strlen，查询指定字符串的长度</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>$strlen，目标字符串长度超出int/long/double最大范围</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>$strlen，指定的目标字段非字符串</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>$strlen，指定的目标字段不存在</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、进入sdb，find({},{&lt;fieldname&gt;:{&lt;$strlen:1&gt;}})查询指定字符串长度，如字符串长度为
+  -214748364、214748364 
+  或
+  -9223372036854775808、9223372036854775807
+  或 
+  -1.7E+308、1.7E+308
+2、检查查询结果</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>查询成功，返回指定字符串长度跟实际字符串个数一致，返回数据正确</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>$strlen，目标字符串包含空格</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、进入sdb，find({},{&lt;fieldname&gt;:{&lt;$strlen:1&gt;}})查询指定字符串长度，指定的目标字符串长度为0
+2、检查查询结果</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、进入sdb，find({},{&lt;fieldname&gt;:{&lt;$strlen:1&gt;}})查询指定字符串长度，指定的目标字符串包含空格
+2、检查查询结果</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>查询成功，返回指定字符串长度为0</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>查询成功，查询的长度包含空格，如"a b"，返回长度为3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、进入sdb，find({},{&lt;fieldname&gt;:{&lt;$strlen:1&gt;}})查询指定字符串长度，指定的目标字符串长度超出int/long/double最大范围
+2、检查查询结果</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、进入sdb，find({},{&lt;fieldname&gt;:{&lt;$strlen:1&gt;}})指定的目标字段非字符串
+2、检查查询结果</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>查询成功，返回结果为null</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>功能说明：返回字符串中字符改变为小写的结果。非字符串类型返回 null。
+格式：find({},{&lt;fieldname&gt;:{&lt;$lower:1&gt;}})，{a:{$lower:1}}中的1作为占位符出现。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>$strlen，指定占位符不为1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、进入sdb，find({},{&lt;fieldname&gt;:{&lt;$strlen:1&gt;}})查询数组内满足条件的子串，指定的目标字段不存在
+2、检查查询结果</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>$lower，指定的字符串包含大写和小写字母</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>$lower，指定的字符串不包含字母</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>$lower，指定的目标字段非字符串类型</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>$lower，指定的目标字段不存在</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>$lower，指定占位符不为1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、进入sdb，find({},{&lt;fieldname&gt;:{&lt;$strlen:1&gt;}})对字段值取绝对值，指定占位符不为1，如：find({},{&lt;fieldname&gt;:{&lt;$strlen:true&gt;}})
+2、检查查询结果</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、进入sdb，find({},{&lt;fieldname&gt;:{&lt;$lower:1&gt;}})查询字符串中字符改变为小写的结果
+2、检查查询结果</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、进入sdb，find({},{&lt;fieldname&gt;:{&lt;$lower:1&gt;}})查询字符串中字符改变为小写的结果，指定的字符串包含大写和小写字母
+2、检查查询结果</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>查询成功，返回的指定字符串中字母均为小写展示</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、进入sdb，find({},{&lt;fieldname&gt;:{&lt;$lower:1&gt;}})查询字符串中字符改变为小写的结果，指定的字符串不包含字母
+2、检查查询结果</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>查询成功，返回的指定字符串跟原字符串一致</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>$lower，指定的字符串包含空格</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、进入sdb，find({},{&lt;fieldname&gt;:{&lt;$lower:1&gt;}})查询字符串中字符改变为小写的结果，指定的字符串包含空格
+2、检查查询结果</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>查询成功，返回的指定字符串中字母均为小写展示，其他字符不变</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、进入sdb，find({},{&lt;fieldname&gt;:{&lt;$lower:1&gt;}})查询字符串中字符改变为小写的结果，指指定的目标字段非字符串类型
+2、检查查询结果</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、进入sdb，find({},{&lt;fieldname&gt;:{&lt;$lower:1&gt;}})对字段值取绝对值，指定占位符不为1，如：find({},{&lt;fieldname&gt;:{&lt;$lower:true&gt;}})
+2、检查查询结果</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>功能说明：返回字符串中字符改变为大写的结果。非字符串类型返回 null。
+格式：find({},{&lt;fieldname&gt;:{&lt;$upper:1&gt;}})，{a:{ $upper:1}}中的1作为占位符出现。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>查询成功，返回的指定字符串中字母均为大写展示，其他字符不变</t>
+  </si>
+  <si>
+    <t>查询成功，返回的指定字符串中字母均为大写展示</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、占位符只要输入标准的bson格式则均执行成功
+2、查询成功，返回的指定字符串中字母均为大写展示</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、占位符只要输入标准的bson格式则均执行成功
+2、查询成功，返回的指定字符串中字母均为小写展示</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、占位符只要输入标准的bson格式则均执行成功
+2、查询成功，返回指定字符串长度跟实际字符串个数一致</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、占位符只要输入标准的bson格式则均执行成功
+2、查询成功，返回为大于该字段值的最小整数值</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、占位符只要输入标准的bson格式则均执行成功
+2、查询成功，返回为小于该字段值的最小整数值，返回数据正确</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>$upper，指定的字符串包含大写和小写字母</t>
+  </si>
+  <si>
+    <t>1、进入sdb，find({},{&lt;fieldname&gt;:{&lt;$upper:1&gt;}})查询字符串中字符改变为小写的结果，指定的字符串包含大写和小写字母
+2、检查查询结果</t>
+  </si>
+  <si>
+    <t>$upper，指定的字符串不包含字母</t>
+  </si>
+  <si>
+    <t>1、进入sdb，find({},{&lt;fieldname&gt;:{&lt;$upper:1&gt;}})查询字符串中字符改变为小写的结果，指定的字符串不包含字母
+2、检查查询结果</t>
+  </si>
+  <si>
+    <t>$upper，指定的字符串包含空格</t>
+  </si>
+  <si>
+    <t>1、进入sdb，find({},{&lt;fieldname&gt;:{&lt;$upper:1&gt;}})查询字符串中字符改变为小写的结果，指定的字符串包含空格
+2、检查查询结果</t>
+  </si>
+  <si>
+    <t>$upper，指定的目标字段非字符串类型</t>
+  </si>
+  <si>
+    <t>1、进入sdb，find({},{&lt;fieldname&gt;:{&lt;$upper:1&gt;}})查询字符串中字符改变为小写的结果，指指定的目标字段非字符串类型
+2、检查查询结果</t>
+  </si>
+  <si>
+    <t>$upper，指定的目标字段不存在</t>
+  </si>
+  <si>
+    <t>1、进入sdb，find({},{&lt;fieldname&gt;:{&lt;$upper:1&gt;}})查询字符串中字符改变为小写的结果
+2、检查查询结果</t>
+  </si>
+  <si>
+    <t>$upper，指定占位符不为1</t>
+  </si>
+  <si>
+    <t>1、进入sdb，find({},{&lt;fieldname&gt;:{&lt;$upper:1&gt;}})对字段值取绝对值，指定占位符不为1，如：find({},{&lt;fieldname&gt;:{&lt;$upper:true&gt;}})
+2、检查查询结果</t>
+  </si>
+  <si>
+    <t>功能说明：去掉字符串左侧开头的空格(或制表符)。非字符串类型返回 null。
+格式：find({},{&lt;fieldname&gt;:{&lt;$ltrim:1&gt;}})，{a:{ $ltrim:1}}中的1作为占位符出现</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、sdb运行正常
+2、sdb已存在domian、CS、CL
+4、sdb已插入待查找的数据</t>
+  </si>
+  <si>
+    <t>1、sdb运行正常
+2、sdb已存在domian、CS、CL
+5、sdb已插入待查找的数据</t>
+  </si>
+  <si>
+    <t>1、sdb运行正常
+2、sdb已存在domian、CS、CL
+6、sdb已插入待查找的数据</t>
+  </si>
+  <si>
+    <t>1、sdb运行正常
+2、sdb已存在domian、CS、CL
+7、sdb已插入待查找的数据</t>
+  </si>
+  <si>
+    <t>1、sdb运行正常
+2、sdb已存在domian、CS、CL
+8、sdb已插入待查找的数据</t>
+  </si>
+  <si>
+    <t>1、sdb运行正常
+2、sdb已存在domian、CS、CL
+9、sdb已插入待查找的数据</t>
+  </si>
+  <si>
+    <t>1、sdb运行正常
+2、sdb已存在domian、CS、CL
+13、sdb已插入待查找的数据</t>
+  </si>
+  <si>
+    <t>1、sdb运行正常
+2、sdb已存在domian、CS、CL
+14、sdb已插入待查找的数据</t>
+  </si>
+  <si>
+    <t>1、sdb运行正常
+2、sdb已存在domian、CS、CL
+15、sdb已插入待查找的数据</t>
+  </si>
+  <si>
+    <t>1、sdb运行正常
+2、sdb已存在domian、CS、CL
+16、sdb已插入待查找的数据</t>
+  </si>
+  <si>
+    <t>1、sdb运行正常
+2、sdb已存在domian、CS、CL
+17、sdb已插入待查找的数据</t>
+  </si>
+  <si>
+    <t>1、sdb运行正常
+2、sdb已存在domian、CS、CL
+18、sdb已插入待查找的数据</t>
+  </si>
+  <si>
+    <t>1、sdb运行正常
+2、sdb已存在domian、CS、CL
+19、sdb已插入待查找的数据</t>
+  </si>
+  <si>
+    <t>$ltrim，去掉字符串左侧开头的空格</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>$ltrim，去掉字符串左侧开头的制表符</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>$ltrim，指定的目标字符串中间/末尾包含空格</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>$ltrim，指定的目标字符串中间/末尾包含制表符</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>$ltrim，指定的目标字符串只包含空格/制表符</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>$ltrim，指定的目标字符串为空</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>$ltrim，指定的目标字段非字符串类型</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>$ltrim，指定的目标字段不存在</t>
+  </si>
+  <si>
+    <t>1、进入sdb，find({},{&lt;fieldname&gt;:{&lt;$ltrim:1&gt;}})查询字符串中字符改变为小写的结果，指指定的目标字段非字符串类型
+2、检查查询结果</t>
+  </si>
+  <si>
+    <t>1、进入sdb，find({},{&lt;fieldname&gt;:{&lt;$ltrim:1&gt;}})查询字符串中字符改变为小写的结果
+2、检查查询结果</t>
+  </si>
+  <si>
+    <t>$ltrim，指定占位符不为1</t>
+  </si>
+  <si>
+    <t>1、进入sdb，find({},{&lt;fieldname&gt;:{&lt;$ltrim:1&gt;}})对字段值取绝对值，指定占位符不为1，如：find({},{&lt;fieldname&gt;:{&lt;$ltrim:true&gt;}})
+2、检查查询结果</t>
   </si>
 </sst>
 </file>
@@ -1255,8 +1610,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="表1" displayName="表1" ref="A1:I102" tableType="xml" totalsRowShown="0" headerRowDxfId="10" dataDxfId="9" connectionId="1">
-  <autoFilter ref="A1:I102"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="表1" displayName="表1" ref="A1:I119" tableType="xml" totalsRowShown="0" headerRowDxfId="10" dataDxfId="9" connectionId="1">
+  <autoFilter ref="A1:I119"/>
   <tableColumns count="9">
     <tableColumn id="1" uniqueName="name" name="name" dataDxfId="8">
       <xmlColumnPr mapId="1" xpath="/testcases/testcase/@name" xmlDataType="string"/>
@@ -1575,7 +1930,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I102"/>
+  <dimension ref="A1:I119"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="38.25" style="1" customWidth="1"/>
@@ -2725,7 +3080,7 @@
         <v>107</v>
       </c>
       <c r="H43" s="2" t="s">
-        <v>85</v>
+        <v>280</v>
       </c>
       <c r="I43" s="4">
         <v>1</v>
@@ -2832,7 +3187,7 @@
         <v>108</v>
       </c>
       <c r="H47" s="2" t="s">
-        <v>85</v>
+        <v>281</v>
       </c>
       <c r="I47" s="4">
         <v>1</v>
@@ -3582,7 +3937,7 @@
     </row>
     <row r="76" spans="1:9" ht="94.5">
       <c r="A76" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="B76" s="2"/>
       <c r="C76" s="1" t="s">
@@ -3609,7 +3964,7 @@
     </row>
     <row r="77" spans="1:9" ht="94.5">
       <c r="A77" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="C77" s="1" t="s">
         <v>22</v>
@@ -3635,7 +3990,7 @@
     </row>
     <row r="78" spans="1:9" ht="67.5">
       <c r="A78" s="2" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="C78" s="1" t="s">
         <v>22</v>
@@ -3661,7 +4016,7 @@
     </row>
     <row r="79" spans="1:9" ht="94.5">
       <c r="A79" s="2" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="C79" s="1" t="s">
         <v>22</v>
@@ -3687,7 +4042,7 @@
     </row>
     <row r="80" spans="1:9" ht="94.5">
       <c r="A80" s="2" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="C80" s="1" t="s">
         <v>22</v>
@@ -3713,7 +4068,7 @@
     </row>
     <row r="81" spans="1:9" ht="67.5">
       <c r="A81" s="2" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="C81" s="1" t="s">
         <v>22</v>
@@ -3739,7 +4094,7 @@
     </row>
     <row r="82" spans="1:9" ht="67.5">
       <c r="A82" s="2" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="B82" s="2"/>
       <c r="C82" s="1" t="s">
@@ -3781,10 +4136,10 @@
         <v>1</v>
       </c>
       <c r="G83" s="2" t="s">
-        <v>228</v>
+        <v>238</v>
       </c>
       <c r="H83" s="2" t="s">
-        <v>82</v>
+        <v>254</v>
       </c>
       <c r="I83" s="4">
         <v>1</v>
@@ -3792,7 +4147,7 @@
     </row>
     <row r="84" spans="1:9" ht="67.5">
       <c r="A84" s="2" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C84" s="1" t="s">
         <v>22</v>
@@ -3807,7 +4162,7 @@
         <v>1</v>
       </c>
       <c r="G84" s="2" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="H84" s="2" t="s">
         <v>46</v>
@@ -3816,8 +4171,13 @@
         <v>1</v>
       </c>
     </row>
-    <row r="85" spans="1:9" ht="54">
-      <c r="A85" s="2"/>
+    <row r="85" spans="1:9" ht="121.5">
+      <c r="A85" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="B85" s="5" t="s">
+        <v>239</v>
+      </c>
       <c r="C85" s="1" t="s">
         <v>22</v>
       </c>
@@ -3830,14 +4190,20 @@
       <c r="F85" s="4">
         <v>1</v>
       </c>
-      <c r="G85" s="2"/>
-      <c r="H85" s="2"/>
+      <c r="G85" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="H85" s="2" t="s">
+        <v>246</v>
+      </c>
       <c r="I85" s="4">
         <v>1</v>
       </c>
     </row>
     <row r="86" spans="1:9" ht="54">
-      <c r="A86" s="2"/>
+      <c r="A86" s="2" t="s">
+        <v>240</v>
+      </c>
       <c r="C86" s="1" t="s">
         <v>22</v>
       </c>
@@ -3850,14 +4216,20 @@
       <c r="F86" s="4">
         <v>1</v>
       </c>
-      <c r="G86" s="2"/>
-      <c r="H86" s="2"/>
+      <c r="G86" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="H86" s="2" t="s">
+        <v>250</v>
+      </c>
       <c r="I86" s="4">
         <v>1</v>
       </c>
     </row>
     <row r="87" spans="1:9" ht="54">
-      <c r="A87" s="2"/>
+      <c r="A87" s="2" t="s">
+        <v>247</v>
+      </c>
       <c r="C87" s="1" t="s">
         <v>22</v>
       </c>
@@ -3870,14 +4242,20 @@
       <c r="F87" s="4">
         <v>1</v>
       </c>
-      <c r="G87" s="2"/>
-      <c r="H87" s="2"/>
+      <c r="G87" s="2" t="s">
+        <v>249</v>
+      </c>
+      <c r="H87" s="2" t="s">
+        <v>251</v>
+      </c>
       <c r="I87" s="4">
         <v>1</v>
       </c>
     </row>
-    <row r="88" spans="1:9" ht="54">
-      <c r="A88" s="2"/>
+    <row r="88" spans="1:9" ht="67.5">
+      <c r="A88" s="2" t="s">
+        <v>242</v>
+      </c>
       <c r="C88" s="1" t="s">
         <v>22</v>
       </c>
@@ -3890,14 +4268,20 @@
       <c r="F88" s="4">
         <v>1</v>
       </c>
-      <c r="G88" s="2"/>
-      <c r="H88" s="2"/>
+      <c r="G88" s="2" t="s">
+        <v>252</v>
+      </c>
+      <c r="H88" s="2" t="s">
+        <v>246</v>
+      </c>
       <c r="I88" s="4">
         <v>1</v>
       </c>
     </row>
     <row r="89" spans="1:9" ht="54">
-      <c r="A89" s="2"/>
+      <c r="A89" s="2" t="s">
+        <v>243</v>
+      </c>
       <c r="C89" s="1" t="s">
         <v>22</v>
       </c>
@@ -3910,14 +4294,20 @@
       <c r="F89" s="4">
         <v>1</v>
       </c>
-      <c r="G89" s="2"/>
-      <c r="H89" s="2"/>
+      <c r="G89" s="2" t="s">
+        <v>253</v>
+      </c>
+      <c r="H89" s="2" t="s">
+        <v>254</v>
+      </c>
       <c r="I89" s="4">
         <v>1</v>
       </c>
     </row>
     <row r="90" spans="1:9" ht="54">
-      <c r="A90" s="2"/>
+      <c r="A90" s="2" t="s">
+        <v>244</v>
+      </c>
       <c r="C90" s="1" t="s">
         <v>22</v>
       </c>
@@ -3930,14 +4320,20 @@
       <c r="F90" s="4">
         <v>1</v>
       </c>
-      <c r="G90" s="2"/>
-      <c r="H90" s="2"/>
+      <c r="G90" s="2" t="s">
+        <v>257</v>
+      </c>
+      <c r="H90" s="2" t="s">
+        <v>46</v>
+      </c>
       <c r="I90" s="4">
         <v>1</v>
       </c>
     </row>
-    <row r="91" spans="1:9" ht="54">
-      <c r="A91" s="2"/>
+    <row r="91" spans="1:9" ht="67.5">
+      <c r="A91" s="2" t="s">
+        <v>256</v>
+      </c>
       <c r="C91" s="1" t="s">
         <v>22</v>
       </c>
@@ -3945,19 +4341,28 @@
         <v>1</v>
       </c>
       <c r="E91" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F91" s="4">
         <v>1</v>
       </c>
-      <c r="G91" s="2"/>
-      <c r="H91" s="2"/>
+      <c r="G91" s="2" t="s">
+        <v>263</v>
+      </c>
+      <c r="H91" s="2" t="s">
+        <v>279</v>
+      </c>
       <c r="I91" s="4">
         <v>1</v>
       </c>
     </row>
-    <row r="92" spans="1:9" ht="54">
-      <c r="A92" s="2"/>
+    <row r="92" spans="1:9" ht="94.5">
+      <c r="A92" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="B92" s="5" t="s">
+        <v>255</v>
+      </c>
       <c r="C92" s="1" t="s">
         <v>22</v>
       </c>
@@ -3970,14 +4375,20 @@
       <c r="F92" s="4">
         <v>1</v>
       </c>
-      <c r="G92" s="2"/>
-      <c r="H92" s="2"/>
+      <c r="G92" s="2" t="s">
+        <v>265</v>
+      </c>
+      <c r="H92" s="2" t="s">
+        <v>266</v>
+      </c>
       <c r="I92" s="4">
         <v>1</v>
       </c>
     </row>
-    <row r="93" spans="1:9" ht="54">
-      <c r="A93" s="2"/>
+    <row r="93" spans="1:9" ht="67.5">
+      <c r="A93" s="2" t="s">
+        <v>259</v>
+      </c>
       <c r="C93" s="1" t="s">
         <v>22</v>
       </c>
@@ -3990,14 +4401,20 @@
       <c r="F93" s="4">
         <v>1</v>
       </c>
-      <c r="G93" s="2"/>
-      <c r="H93" s="2"/>
+      <c r="G93" s="2" t="s">
+        <v>267</v>
+      </c>
+      <c r="H93" s="2" t="s">
+        <v>268</v>
+      </c>
       <c r="I93" s="4">
         <v>1</v>
       </c>
     </row>
     <row r="94" spans="1:9" ht="54">
-      <c r="A94" s="2"/>
+      <c r="A94" s="2" t="s">
+        <v>269</v>
+      </c>
       <c r="C94" s="1" t="s">
         <v>22</v>
       </c>
@@ -4010,14 +4427,20 @@
       <c r="F94" s="4">
         <v>1</v>
       </c>
-      <c r="G94" s="2"/>
-      <c r="H94" s="2"/>
+      <c r="G94" s="2" t="s">
+        <v>270</v>
+      </c>
+      <c r="H94" s="2" t="s">
+        <v>271</v>
+      </c>
       <c r="I94" s="4">
         <v>1</v>
       </c>
     </row>
-    <row r="95" spans="1:9" ht="54">
-      <c r="A95" s="2"/>
+    <row r="95" spans="1:9" ht="67.5">
+      <c r="A95" s="2" t="s">
+        <v>260</v>
+      </c>
       <c r="C95" s="1" t="s">
         <v>22</v>
       </c>
@@ -4030,14 +4453,20 @@
       <c r="F95" s="4">
         <v>1</v>
       </c>
-      <c r="G95" s="2"/>
-      <c r="H95" s="2"/>
+      <c r="G95" s="2" t="s">
+        <v>272</v>
+      </c>
+      <c r="H95" s="2" t="s">
+        <v>254</v>
+      </c>
       <c r="I95" s="4">
         <v>1</v>
       </c>
     </row>
     <row r="96" spans="1:9" ht="54">
-      <c r="A96" s="2"/>
+      <c r="A96" s="2" t="s">
+        <v>261</v>
+      </c>
       <c r="C96" s="1" t="s">
         <v>22</v>
       </c>
@@ -4050,14 +4479,20 @@
       <c r="F96" s="4">
         <v>1</v>
       </c>
-      <c r="G96" s="2"/>
-      <c r="H96" s="2"/>
+      <c r="G96" s="2" t="s">
+        <v>264</v>
+      </c>
+      <c r="H96" s="2" t="s">
+        <v>46</v>
+      </c>
       <c r="I96" s="4">
         <v>1</v>
       </c>
     </row>
-    <row r="97" spans="1:9" ht="54">
-      <c r="A97" s="2"/>
+    <row r="97" spans="1:9" ht="67.5">
+      <c r="A97" s="2" t="s">
+        <v>262</v>
+      </c>
       <c r="C97" s="1" t="s">
         <v>22</v>
       </c>
@@ -4065,19 +4500,28 @@
         <v>1</v>
       </c>
       <c r="E97" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F97" s="4">
         <v>1</v>
       </c>
-      <c r="G97" s="2"/>
-      <c r="H97" s="2"/>
+      <c r="G97" s="2" t="s">
+        <v>273</v>
+      </c>
+      <c r="H97" s="2" t="s">
+        <v>278</v>
+      </c>
       <c r="I97" s="4">
         <v>1</v>
       </c>
     </row>
-    <row r="98" spans="1:9" ht="54">
-      <c r="A98" s="2"/>
+    <row r="98" spans="1:9" ht="94.5">
+      <c r="A98" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="B98" s="5" t="s">
+        <v>274</v>
+      </c>
       <c r="C98" s="1" t="s">
         <v>22</v>
       </c>
@@ -4090,14 +4534,20 @@
       <c r="F98" s="4">
         <v>1</v>
       </c>
-      <c r="G98" s="2"/>
-      <c r="H98" s="2"/>
+      <c r="G98" s="2" t="s">
+        <v>283</v>
+      </c>
+      <c r="H98" s="2" t="s">
+        <v>276</v>
+      </c>
       <c r="I98" s="4">
         <v>1</v>
       </c>
     </row>
-    <row r="99" spans="1:9" ht="54">
-      <c r="A99" s="2"/>
+    <row r="99" spans="1:9" ht="67.5">
+      <c r="A99" s="2" t="s">
+        <v>284</v>
+      </c>
       <c r="C99" s="1" t="s">
         <v>22</v>
       </c>
@@ -4110,14 +4560,20 @@
       <c r="F99" s="4">
         <v>1</v>
       </c>
-      <c r="G99" s="2"/>
-      <c r="H99" s="2"/>
+      <c r="G99" s="2" t="s">
+        <v>285</v>
+      </c>
+      <c r="H99" s="2" t="s">
+        <v>268</v>
+      </c>
       <c r="I99" s="4">
         <v>1</v>
       </c>
     </row>
     <row r="100" spans="1:9" ht="54">
-      <c r="A100" s="2"/>
+      <c r="A100" s="2" t="s">
+        <v>286</v>
+      </c>
       <c r="C100" s="1" t="s">
         <v>22</v>
       </c>
@@ -4130,14 +4586,20 @@
       <c r="F100" s="4">
         <v>1</v>
       </c>
-      <c r="G100" s="2"/>
-      <c r="H100" s="2"/>
+      <c r="G100" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="H100" s="2" t="s">
+        <v>275</v>
+      </c>
       <c r="I100" s="4">
         <v>1</v>
       </c>
     </row>
-    <row r="101" spans="1:9" ht="54">
-      <c r="A101" s="2"/>
+    <row r="101" spans="1:9" ht="67.5">
+      <c r="A101" s="2" t="s">
+        <v>288</v>
+      </c>
       <c r="C101" s="1" t="s">
         <v>22</v>
       </c>
@@ -4150,22 +4612,389 @@
       <c r="F101" s="4">
         <v>1</v>
       </c>
-      <c r="G101" s="2"/>
-      <c r="H101" s="2"/>
+      <c r="G101" s="2" t="s">
+        <v>289</v>
+      </c>
+      <c r="H101" s="2" t="s">
+        <v>254</v>
+      </c>
       <c r="I101" s="4">
         <v>1</v>
       </c>
     </row>
-    <row r="102" spans="1:9">
-      <c r="A102" s="4"/>
-      <c r="B102" s="6"/>
-      <c r="C102" s="4"/>
-      <c r="D102" s="4"/>
-      <c r="E102" s="4"/>
-      <c r="F102" s="4"/>
-      <c r="G102" s="2"/>
-      <c r="H102" s="4"/>
-      <c r="I102" s="4"/>
+    <row r="102" spans="1:9" ht="54">
+      <c r="A102" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="C102" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D102" s="4">
+        <v>1</v>
+      </c>
+      <c r="E102" s="4">
+        <v>2</v>
+      </c>
+      <c r="F102" s="4">
+        <v>1</v>
+      </c>
+      <c r="G102" s="2" t="s">
+        <v>291</v>
+      </c>
+      <c r="H102" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="I102" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="103" spans="1:9" ht="67.5">
+      <c r="A103" s="2" t="s">
+        <v>292</v>
+      </c>
+      <c r="C103" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D103" s="4">
+        <v>1</v>
+      </c>
+      <c r="E103" s="4">
+        <v>1</v>
+      </c>
+      <c r="F103" s="4">
+        <v>1</v>
+      </c>
+      <c r="G103" s="2" t="s">
+        <v>293</v>
+      </c>
+      <c r="H103" s="2" t="s">
+        <v>277</v>
+      </c>
+      <c r="I103" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="104" spans="1:9" ht="94.5">
+      <c r="A104" s="4" t="s">
+        <v>308</v>
+      </c>
+      <c r="B104" s="6" t="s">
+        <v>294</v>
+      </c>
+      <c r="C104" s="1" t="s">
+        <v>295</v>
+      </c>
+      <c r="D104" s="4">
+        <v>1</v>
+      </c>
+      <c r="E104" s="4">
+        <v>1</v>
+      </c>
+      <c r="F104" s="4">
+        <v>1</v>
+      </c>
+      <c r="G104" s="2"/>
+      <c r="H104" s="4"/>
+      <c r="I104" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="105" spans="1:9" ht="54">
+      <c r="A105" s="4" t="s">
+        <v>309</v>
+      </c>
+      <c r="C105" s="1" t="s">
+        <v>296</v>
+      </c>
+      <c r="D105" s="4">
+        <v>1</v>
+      </c>
+      <c r="E105" s="4">
+        <v>1</v>
+      </c>
+      <c r="F105" s="4">
+        <v>1</v>
+      </c>
+      <c r="I105" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="106" spans="1:9" ht="54">
+      <c r="A106" s="4" t="s">
+        <v>310</v>
+      </c>
+      <c r="C106" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="D106" s="4">
+        <v>1</v>
+      </c>
+      <c r="E106" s="4">
+        <v>1</v>
+      </c>
+      <c r="F106" s="4">
+        <v>1</v>
+      </c>
+      <c r="I106" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="107" spans="1:9" ht="54">
+      <c r="A107" s="4" t="s">
+        <v>311</v>
+      </c>
+      <c r="C107" s="1" t="s">
+        <v>298</v>
+      </c>
+      <c r="D107" s="4">
+        <v>1</v>
+      </c>
+      <c r="E107" s="4">
+        <v>1</v>
+      </c>
+      <c r="F107" s="4">
+        <v>1</v>
+      </c>
+      <c r="I107" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="108" spans="1:9" ht="54">
+      <c r="A108" s="4" t="s">
+        <v>312</v>
+      </c>
+      <c r="C108" s="1" t="s">
+        <v>299</v>
+      </c>
+      <c r="D108" s="4">
+        <v>1</v>
+      </c>
+      <c r="E108" s="4">
+        <v>1</v>
+      </c>
+      <c r="F108" s="4">
+        <v>1</v>
+      </c>
+      <c r="I108" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="109" spans="1:9" ht="54">
+      <c r="A109" s="4" t="s">
+        <v>313</v>
+      </c>
+      <c r="C109" s="1" t="s">
+        <v>300</v>
+      </c>
+      <c r="D109" s="4">
+        <v>1</v>
+      </c>
+      <c r="E109" s="4">
+        <v>1</v>
+      </c>
+      <c r="F109" s="4">
+        <v>1</v>
+      </c>
+      <c r="I109" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="110" spans="1:9" ht="67.5">
+      <c r="A110" s="2" t="s">
+        <v>314</v>
+      </c>
+      <c r="C110" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D110" s="4">
+        <v>1</v>
+      </c>
+      <c r="E110" s="4">
+        <v>2</v>
+      </c>
+      <c r="F110" s="4">
+        <v>1</v>
+      </c>
+      <c r="G110" s="2" t="s">
+        <v>316</v>
+      </c>
+      <c r="H110" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="I110" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="111" spans="1:9" ht="54">
+      <c r="A111" s="2" t="s">
+        <v>315</v>
+      </c>
+      <c r="C111" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D111" s="4">
+        <v>1</v>
+      </c>
+      <c r="E111" s="4">
+        <v>2</v>
+      </c>
+      <c r="F111" s="4">
+        <v>1</v>
+      </c>
+      <c r="G111" s="2" t="s">
+        <v>317</v>
+      </c>
+      <c r="H111" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="I111" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="112" spans="1:9" ht="67.5">
+      <c r="A112" s="2" t="s">
+        <v>318</v>
+      </c>
+      <c r="C112" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D112" s="4">
+        <v>1</v>
+      </c>
+      <c r="E112" s="4">
+        <v>1</v>
+      </c>
+      <c r="F112" s="4">
+        <v>1</v>
+      </c>
+      <c r="G112" s="2" t="s">
+        <v>319</v>
+      </c>
+      <c r="H112" s="2" t="s">
+        <v>277</v>
+      </c>
+      <c r="I112" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="113" spans="3:9" ht="54">
+      <c r="C113" s="1" t="s">
+        <v>301</v>
+      </c>
+      <c r="D113" s="4">
+        <v>1</v>
+      </c>
+      <c r="E113" s="4">
+        <v>1</v>
+      </c>
+      <c r="F113" s="4">
+        <v>1</v>
+      </c>
+      <c r="I113" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="114" spans="3:9" ht="54">
+      <c r="C114" s="1" t="s">
+        <v>302</v>
+      </c>
+      <c r="D114" s="4">
+        <v>1</v>
+      </c>
+      <c r="E114" s="4">
+        <v>1</v>
+      </c>
+      <c r="F114" s="4">
+        <v>1</v>
+      </c>
+      <c r="I114" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="115" spans="3:9" ht="54">
+      <c r="C115" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="D115" s="4">
+        <v>1</v>
+      </c>
+      <c r="E115" s="4">
+        <v>1</v>
+      </c>
+      <c r="F115" s="4">
+        <v>1</v>
+      </c>
+      <c r="I115" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="116" spans="3:9" ht="54">
+      <c r="C116" s="1" t="s">
+        <v>304</v>
+      </c>
+      <c r="D116" s="4">
+        <v>1</v>
+      </c>
+      <c r="E116" s="4">
+        <v>1</v>
+      </c>
+      <c r="F116" s="4">
+        <v>1</v>
+      </c>
+      <c r="I116" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="117" spans="3:9" ht="54">
+      <c r="C117" s="1" t="s">
+        <v>305</v>
+      </c>
+      <c r="D117" s="4">
+        <v>1</v>
+      </c>
+      <c r="E117" s="4">
+        <v>1</v>
+      </c>
+      <c r="F117" s="4">
+        <v>1</v>
+      </c>
+      <c r="I117" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="118" spans="3:9" ht="54">
+      <c r="C118" s="1" t="s">
+        <v>306</v>
+      </c>
+      <c r="D118" s="4">
+        <v>1</v>
+      </c>
+      <c r="E118" s="4">
+        <v>1</v>
+      </c>
+      <c r="F118" s="4">
+        <v>1</v>
+      </c>
+      <c r="I118" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="119" spans="3:9" ht="54">
+      <c r="C119" s="1" t="s">
+        <v>307</v>
+      </c>
+      <c r="D119" s="4">
+        <v>1</v>
+      </c>
+      <c r="E119" s="4">
+        <v>1</v>
+      </c>
+      <c r="F119" s="4">
+        <v>1</v>
+      </c>
+      <c r="I119" s="4">
+        <v>1</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/internal_doc/05.测试设计/story/selector/Story-selector测试用例.xlsx
+++ b/internal_doc/05.测试设计/story/selector/Story-selector测试用例.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="470" uniqueCount="320">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="646" uniqueCount="424">
   <si>
     <t>name</t>
   </si>
@@ -1350,71 +1350,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>1、sdb运行正常
-2、sdb已存在domian、CS、CL
-4、sdb已插入待查找的数据</t>
-  </si>
-  <si>
-    <t>1、sdb运行正常
-2、sdb已存在domian、CS、CL
-5、sdb已插入待查找的数据</t>
-  </si>
-  <si>
-    <t>1、sdb运行正常
-2、sdb已存在domian、CS、CL
-6、sdb已插入待查找的数据</t>
-  </si>
-  <si>
-    <t>1、sdb运行正常
-2、sdb已存在domian、CS、CL
-7、sdb已插入待查找的数据</t>
-  </si>
-  <si>
-    <t>1、sdb运行正常
-2、sdb已存在domian、CS、CL
-8、sdb已插入待查找的数据</t>
-  </si>
-  <si>
-    <t>1、sdb运行正常
-2、sdb已存在domian、CS、CL
-9、sdb已插入待查找的数据</t>
-  </si>
-  <si>
-    <t>1、sdb运行正常
-2、sdb已存在domian、CS、CL
-13、sdb已插入待查找的数据</t>
-  </si>
-  <si>
-    <t>1、sdb运行正常
-2、sdb已存在domian、CS、CL
-14、sdb已插入待查找的数据</t>
-  </si>
-  <si>
-    <t>1、sdb运行正常
-2、sdb已存在domian、CS、CL
-15、sdb已插入待查找的数据</t>
-  </si>
-  <si>
-    <t>1、sdb运行正常
-2、sdb已存在domian、CS、CL
-16、sdb已插入待查找的数据</t>
-  </si>
-  <si>
-    <t>1、sdb运行正常
-2、sdb已存在domian、CS、CL
-17、sdb已插入待查找的数据</t>
-  </si>
-  <si>
-    <t>1、sdb运行正常
-2、sdb已存在domian、CS、CL
-18、sdb已插入待查找的数据</t>
-  </si>
-  <si>
-    <t>1、sdb运行正常
-2、sdb已存在domian、CS、CL
-19、sdb已插入待查找的数据</t>
-  </si>
-  <si>
     <t>$ltrim，去掉字符串左侧开头的空格</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1446,19 +1381,467 @@
     <t>$ltrim，指定的目标字段不存在</t>
   </si>
   <si>
-    <t>1、进入sdb，find({},{&lt;fieldname&gt;:{&lt;$ltrim:1&gt;}})查询字符串中字符改变为小写的结果，指指定的目标字段非字符串类型
-2、检查查询结果</t>
-  </si>
-  <si>
-    <t>1、进入sdb，find({},{&lt;fieldname&gt;:{&lt;$ltrim:1&gt;}})查询字符串中字符改变为小写的结果
-2、检查查询结果</t>
-  </si>
-  <si>
     <t>$ltrim，指定占位符不为1</t>
   </si>
   <si>
-    <t>1、进入sdb，find({},{&lt;fieldname&gt;:{&lt;$ltrim:1&gt;}})对字段值取绝对值，指定占位符不为1，如：find({},{&lt;fieldname&gt;:{&lt;$ltrim:true&gt;}})
-2、检查查询结果</t>
+    <t>1、进入sdb，find({},{&lt;fieldname&gt;:{&lt;$ltrim:1&gt;}})去掉字符串左侧开头的空格(或制表符)，指定的字符串左侧以空格开头
+2、检查查询结果</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>查询成功，返回的指定字符串中左侧空格被去掉，返回结果正确</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、进入sdb，find({},{&lt;fieldname&gt;:{&lt;$ltrim:1&gt;}})去掉字符串左侧开头的空格(或制表符)，指定的字符串左侧以制表符开头
+2、检查查询结果</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>$ltrim，指定的目标字符串左侧开头包含空格和制表符</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>查询成功，返回的指定字符串中左侧制表符被去掉，返回结果正确</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、进入sdb，find({},{&lt;fieldname&gt;:{&lt;$ltrim:1&gt;}})去掉字符串左侧开头的空格(或制表符)，指定的目标字符串左侧开头包含空格和制表符
+2、检查查询结果</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>查询成功，返回的指定字符串中左侧的空格和制表符都被去掉，返回结果正确</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、进入sdb，find({},{&lt;fieldname&gt;:{&lt;$ltrim:1&gt;}})去掉字符串左侧开头的空格(或制表符)，指定的目标字符串中间/末尾包含空格
+2、检查查询结果</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>查询成功，指定的目标字符串中间/末尾包含的空格不会被去掉，返回结果正确</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、进入sdb，find({},{&lt;fieldname&gt;:{&lt;$ltrim:1&gt;}})去掉字符串左侧开头的空格(或制表符)，指定的目标字符串中间/末尾包含制表符
+2、检查查询结果</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>查询成功，指定的目标字符串中间/末尾包含的制表符不会被去掉，返回结果正确</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、进入sdb，find({},{&lt;fieldname&gt;:{&lt;$ltrim:1&gt;}})去掉字符串左侧开头的空格(或制表符)，指定的目标字符串只包含空格/制表符
+2、检查查询结果</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>查询成功，返回的字符串为null</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、进入sdb，find({},{&lt;fieldname&gt;:{&lt;$ltrim:1&gt;}})去掉字符串左侧开头的空格(或制表符)，指定的目标字符串为空
+2、检查查询结果</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、进入sdb，find({},{&lt;fieldname&gt;:{&lt;$ltrim:1&gt;}})去掉字符串左侧开头的空格(或制表符)，指指定的目标字段非字符串类型
+2、检查查询结果</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、进入sdb，find({},{&lt;fieldname&gt;:{&lt;$ltrim:1&gt;}})去掉字符串左侧开头的空格(或制表符)
+2、检查查询结果</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、进入sdb，find({},{&lt;fieldname&gt;:{&lt;$ltrim:1&gt;}})去掉字符串左侧开头的空格(或制表符)，指定占位符不为1，如：find({},{&lt;fieldname&gt;:{&lt;$ltrim:true&gt;}})
+2、检查查询结果</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、占位符只要输入标准的bson格式则均执行成功
+2、查询成功，去掉字符串左侧开头的空格(或制表符)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>功能说明：去掉字符串右侧开头的空格(及制表符)。非字符串类型返回 null。
+格式：find({},{&lt;fieldname&gt;:{&lt;$rtrim:1&gt;}})，{a:{$rtrim:1}}中的1作为占位符出现。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>$rtrim，指定的目标字符串中间/末尾包含空格</t>
+  </si>
+  <si>
+    <t>$rtrim，指定的目标字符串中间/末尾包含制表符</t>
+  </si>
+  <si>
+    <t>$rtrim，指定的目标字符串只包含空格/制表符</t>
+  </si>
+  <si>
+    <t>$rtrim，指定的目标字符串为空</t>
+  </si>
+  <si>
+    <t>$rtrim，指定的目标字段非字符串类型</t>
+  </si>
+  <si>
+    <t>$rtrim，指定的目标字段不存在</t>
+  </si>
+  <si>
+    <t>$rtrim，指定占位符不为1</t>
+  </si>
+  <si>
+    <t>1、进入sdb，find({},{&lt;fieldname&gt;:{&lt;$rtrim:1&gt;}})去掉字符串右侧开头的空格(或制表符)，指定的字符串右侧以空格开头
+2、检查查询结果</t>
+  </si>
+  <si>
+    <t>查询成功，返回的指定字符串中右侧空格被去掉，返回结果正确</t>
+  </si>
+  <si>
+    <t>$rtrim，去掉字符串右侧开头的制表符</t>
+  </si>
+  <si>
+    <t>1、进入sdb，find({},{&lt;fieldname&gt;:{&lt;$rtrim:1&gt;}})去掉字符串右侧开头的空格(或制表符)，指定的字符串右侧以制表符开头
+2、检查查询结果</t>
+  </si>
+  <si>
+    <t>查询成功，返回的指定字符串中右侧制表符被去掉，返回结果正确</t>
+  </si>
+  <si>
+    <t>$rtrim，指定的目标字符串右侧开头包含空格和制表符</t>
+  </si>
+  <si>
+    <t>1、进入sdb，find({},{&lt;fieldname&gt;:{&lt;$rtrim:1&gt;}})去掉字符串右侧开头的空格(或制表符)，指定的目标字符串右侧开头包含空格和制表符
+2、检查查询结果</t>
+  </si>
+  <si>
+    <t>查询成功，返回的指定字符串中右侧的空格和制表符都被去掉，返回结果正确</t>
+  </si>
+  <si>
+    <t>1、进入sdb，find({},{&lt;fieldname&gt;:{&lt;$rtrim:1&gt;}})去掉字符串右侧开头的空格(或制表符)，指定的目标字符串中间/末尾包含空格
+2、检查查询结果</t>
+  </si>
+  <si>
+    <t>1、进入sdb，find({},{&lt;fieldname&gt;:{&lt;$rtrim:1&gt;}})去掉字符串右侧开头的空格(或制表符)，指定的目标字符串中间/末尾包含制表符
+2、检查查询结果</t>
+  </si>
+  <si>
+    <t>1、进入sdb，find({},{&lt;fieldname&gt;:{&lt;$rtrim:1&gt;}})去掉字符串右侧开头的空格(或制表符)，指定的目标字符串只包含空格/制表符
+2、检查查询结果</t>
+  </si>
+  <si>
+    <t>1、进入sdb，find({},{&lt;fieldname&gt;:{&lt;$rtrim:1&gt;}})去掉字符串右侧开头的空格(或制表符)，指定的目标字符串为空
+2、检查查询结果</t>
+  </si>
+  <si>
+    <t>1、进入sdb，find({},{&lt;fieldname&gt;:{&lt;$rtrim:1&gt;}})去掉字符串右侧开头的空格(或制表符)，指指定的目标字段非字符串类型
+2、检查查询结果</t>
+  </si>
+  <si>
+    <t>1、进入sdb，find({},{&lt;fieldname&gt;:{&lt;$rtrim:1&gt;}})去掉字符串右侧开头的空格(或制表符)
+2、检查查询结果</t>
+  </si>
+  <si>
+    <t>1、进入sdb，find({},{&lt;fieldname&gt;:{&lt;$rtrim:1&gt;}})去掉字符串右侧开头的空格(或制表符)，指定占位符不为1，如：find({},{&lt;fieldname&gt;:{&lt;$rtrim:true&gt;}})
+2、检查查询结果</t>
+  </si>
+  <si>
+    <t>1、占位符只要输入标准的bson格式则均执行成功
+2、查询成功，去掉字符串右侧开头的空格(或制表符)</t>
+  </si>
+  <si>
+    <t>$rtrim，去掉字符串右侧开头的空格</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>查询成功，返回的指定字符串中两侧空格被去掉，返回结果正确</t>
+  </si>
+  <si>
+    <t>查询成功，返回的指定字符串中两侧制表符被去掉，返回结果正确</t>
+  </si>
+  <si>
+    <t>查询成功，返回的指定字符串中两侧的空格和制表符都被去掉，返回结果正确</t>
+  </si>
+  <si>
+    <t>1、占位符只要输入标准的bson格式则均执行成功
+2、查询成功，去掉字符串两侧开头的空格(或制表符)</t>
+  </si>
+  <si>
+    <t>功能说明：去掉字符串两侧开头的空格(及制表符)。非字符串类型返回 null。
+格式：find({},{&lt;fieldname&gt;:{&lt;$trim:1&gt;}})，{a:{ $trim:1}}中的1作为占位符出现。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>$trim，去掉字符串两侧开头的空格</t>
+  </si>
+  <si>
+    <t>1、进入sdb，find({},{&lt;fieldname&gt;:{&lt;$trim:1&gt;}})去掉字符串两侧开头的空格(或制表符)，指定的字符串两侧以空格开头
+2、检查查询结果</t>
+  </si>
+  <si>
+    <t>$trim，去掉字符串两侧开头的制表符</t>
+  </si>
+  <si>
+    <t>1、进入sdb，find({},{&lt;fieldname&gt;:{&lt;$trim:1&gt;}})去掉字符串两侧开头的空格(或制表符)，指定的字符串两侧以制表符开头
+2、检查查询结果</t>
+  </si>
+  <si>
+    <t>$trim，指定的目标字符串两侧开头包含空格和制表符</t>
+  </si>
+  <si>
+    <t>1、进入sdb，find({},{&lt;fieldname&gt;:{&lt;$trim:1&gt;}})去掉字符串两侧开头的空格(或制表符)，指定的目标字符串两侧开头包含空格和制表符
+2、检查查询结果</t>
+  </si>
+  <si>
+    <t>$trim，指定的目标字符串中间/末尾包含空格</t>
+  </si>
+  <si>
+    <t>1、进入sdb，find({},{&lt;fieldname&gt;:{&lt;$trim:1&gt;}})去掉字符串两侧开头的空格(或制表符)，指定的目标字符串中间/末尾包含空格
+2、检查查询结果</t>
+  </si>
+  <si>
+    <t>$trim，指定的目标字符串中间/末尾包含制表符</t>
+  </si>
+  <si>
+    <t>1、进入sdb，find({},{&lt;fieldname&gt;:{&lt;$trim:1&gt;}})去掉字符串两侧开头的空格(或制表符)，指定的目标字符串中间/末尾包含制表符
+2、检查查询结果</t>
+  </si>
+  <si>
+    <t>$trim，指定的目标字符串只包含空格/制表符</t>
+  </si>
+  <si>
+    <t>1、进入sdb，find({},{&lt;fieldname&gt;:{&lt;$trim:1&gt;}})去掉字符串两侧开头的空格(或制表符)，指定的目标字符串只包含空格/制表符
+2、检查查询结果</t>
+  </si>
+  <si>
+    <t>$trim，指定的目标字符串为空</t>
+  </si>
+  <si>
+    <t>1、进入sdb，find({},{&lt;fieldname&gt;:{&lt;$trim:1&gt;}})去掉字符串两侧开头的空格(或制表符)，指定的目标字符串为空
+2、检查查询结果</t>
+  </si>
+  <si>
+    <t>$trim，指定的目标字段非字符串类型</t>
+  </si>
+  <si>
+    <t>1、进入sdb，find({},{&lt;fieldname&gt;:{&lt;$trim:1&gt;}})去掉字符串两侧开头的空格(或制表符)，指指定的目标字段非字符串类型
+2、检查查询结果</t>
+  </si>
+  <si>
+    <t>$trim，指定的目标字段不存在</t>
+  </si>
+  <si>
+    <t>1、进入sdb，find({},{&lt;fieldname&gt;:{&lt;$trim:1&gt;}})去掉字符串两侧开头的空格(或制表符)
+2、检查查询结果</t>
+  </si>
+  <si>
+    <t>$trim，指定占位符不为1</t>
+  </si>
+  <si>
+    <t>1、进入sdb，find({},{&lt;fieldname&gt;:{&lt;$trim:1&gt;}})去掉字符串两侧开头的空格(或制表符)，指定占位符不为1，如：find({},{&lt;fieldname&gt;:{&lt;$trim:true&gt;}})
+2、检查查询结果</t>
+  </si>
+  <si>
+    <t>$cast，将指定字段转换为MinKey类型，有效转换</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>功能说明：将字段转化为指定类型。其中指定的类型可以使用字符串表示(大小写不敏感)，也可以使用数字表示。时间类型字段转换为Int32类型可能会发生溢出。
+格式：find({},{&lt;fieldname&gt;:{&lt;$cast:type&gt;}})。
+支持转换为MinKey的源数据类型为：ALL，即：MinKey Double Object ObjectId Bool Date Int32 Timestamp Int64 MaxKey String</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>$cast，将指定字段转换为Double类型，有效转换</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>$cast，将指定字段转换为Double类型，无效转换</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>支持转换为Double的源数据类型为：String Bool Int32 Int64 Double</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>不支持转换为Double的源数据类型为：MinKey Double Object ObjectId Date Timestamp MaxKey</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>$cast，将指定字段转换为String类型，无效转换</t>
+  </si>
+  <si>
+    <t>不支持转换为String的源数据类型为：String ObjectId Bool MinKey MaxKey</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>$cast，将指定字段转换为Object类型，无效转换</t>
+  </si>
+  <si>
+    <t>不支持转换为Object的源数据类型为：MinKey Double Object ObjectId Bool Date Int32 Timestamp Int64 MaxKey</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>$cast，将指定字段转换为Object类型，有效转换</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>支持转换为Object的源数据类型为：String Object</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>$cast，将指定字段转换为String类型，有效转换</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>支持转换为String的源数据类型为：Int32 Int64 Double Date Timestamp Oid Object Array String</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>$cast，将指定字段转换为ObjectId类型，无效转换</t>
+  </si>
+  <si>
+    <t>$cast，将指定字段转换为ObjectId类型，有效转换</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>不支持转换为ObjectId的源数据类型为：MinKey Double Object ObjectId Bool Date Int32 Timestamp Int64 MaxKey</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>支持转换为ObjectId的源数据类型为：String ObjectId</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>$cast，将指定字段转换为Bool类型，无效转换</t>
+  </si>
+  <si>
+    <t>$cast，将指定字段转换为Bool类型，有效转换</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>支持转换为Bool的源数据类型为：Int32 Int64 Double Bool</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>不支持转换为Bool的源数据类型为：MinKey String Object ObjectId Bool Date Timestamp MaxKey</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>$cast，将指定字段转换为Date类型，有效转换</t>
+  </si>
+  <si>
+    <t>$cast，将指定字段转换为Date类型，无效转换</t>
+  </si>
+  <si>
+    <t>支持转换为Date的源数据类型为：Int64 Double Stirng Timestamp Int32</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>不支持转换为Date的源数据类型为：MinKey Object ObjectId Bool Date MaxKey</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>$cast，将指定字段转换为Null类型，有效转换</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>支持转换为Null的源数据类型为：ALL，即：MinKey Double Object ObjectId Bool Date Int32 Timestamp Int64 MaxKey String</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>$cast，将指定字段转换为Int32类型，无效转换</t>
+  </si>
+  <si>
+    <t>$cast，将指定字段转换为Int32类型，有效转换</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>$cast，将指定字段转换为Timestamp类型，无效转换</t>
+  </si>
+  <si>
+    <t>$cast，将指定字段转换为Timestamp类型，有效转换</t>
+  </si>
+  <si>
+    <t>支持转换为Int32的源数据类型为：Int32 Double Object ObjectId Date Timestamp MaxKey</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>不支持转换为Int32的源数据类型为：MinKey Object ObjectId Int32 MaxKey</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>支持转换为Timestamp的源数据类型为：Int32 Int64 Double Stirng Date Timestamp</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>不支持转换为Timestamp的源数据类型为：MinKey Object ObjectId Bool Timestamp MaxKey</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>$cast，将指定字段转换为Int64类型，无效转换</t>
+  </si>
+  <si>
+    <t>不支持转换为Int64的源数据类型为：MinKey Object ObjectId Bool Int64 MaxKey</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>$cast，将指定字段转换为Int64类型，有效转换</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>支持转换为Int64的源数据类型为：Int32 Double Stirng Timestamp Date Int64</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>$cast，将指定字段转换为MaxKey类型，有效转换</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>支持转换为MaxKey的源数据类型为：ALL，即：MinKey Double Object ObjectId Bool Date Int32 Timestamp Int64 MaxKey String</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>$cast，指定的目标类型为全小写</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>$cast，指定的目标类型为全大写/全小写/大小混写</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>$cast，指定的字段源类型为不支持转换的其他数据类型（表里面没有列出的其他类型）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>如regex、binary</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>$cast，指定的目标类型用字符串表示</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>$cast，指定的目标类型用数字表示</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>$cast，指定的目标类型字符串非法</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>$cast，指定的目标类型用数字非法</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>$cast，指定的目标类型为不支持转换的其他数据类型（表里面没有列出的其他类型）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>$cast，指定的字段不存在</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -1610,8 +1993,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="表1" displayName="表1" ref="A1:I119" tableType="xml" totalsRowShown="0" headerRowDxfId="10" dataDxfId="9" connectionId="1">
-  <autoFilter ref="A1:I119"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="表1" displayName="表1" ref="A1:I164" tableType="xml" totalsRowShown="0" headerRowDxfId="10" dataDxfId="9" connectionId="1">
+  <autoFilter ref="A1:I164"/>
   <tableColumns count="9">
     <tableColumn id="1" uniqueName="name" name="name" dataDxfId="8">
       <xmlColumnPr mapId="1" xpath="/testcases/testcase/@name" xmlDataType="string"/>
@@ -1930,7 +2313,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I119"/>
+  <dimension ref="A1:I164"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="38.25" style="1" customWidth="1"/>
@@ -4676,13 +5059,13 @@
     </row>
     <row r="104" spans="1:9" ht="94.5">
       <c r="A104" s="4" t="s">
-        <v>308</v>
+        <v>295</v>
       </c>
       <c r="B104" s="6" t="s">
         <v>294</v>
       </c>
       <c r="C104" s="1" t="s">
-        <v>295</v>
+        <v>22</v>
       </c>
       <c r="D104" s="4">
         <v>1</v>
@@ -4693,116 +5076,150 @@
       <c r="F104" s="4">
         <v>1</v>
       </c>
-      <c r="G104" s="2"/>
-      <c r="H104" s="4"/>
+      <c r="G104" s="2" t="s">
+        <v>304</v>
+      </c>
+      <c r="H104" s="2" t="s">
+        <v>305</v>
+      </c>
       <c r="I104" s="4">
         <v>1</v>
       </c>
     </row>
-    <row r="105" spans="1:9" ht="54">
+    <row r="105" spans="1:9" ht="67.5">
       <c r="A105" s="4" t="s">
+        <v>296</v>
+      </c>
+      <c r="C105" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D105" s="4">
+        <v>1</v>
+      </c>
+      <c r="E105" s="4">
+        <v>1</v>
+      </c>
+      <c r="F105" s="4">
+        <v>1</v>
+      </c>
+      <c r="G105" s="2" t="s">
+        <v>306</v>
+      </c>
+      <c r="H105" s="2" t="s">
+        <v>308</v>
+      </c>
+      <c r="I105" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="106" spans="1:9" ht="67.5">
+      <c r="A106" s="4" t="s">
+        <v>307</v>
+      </c>
+      <c r="C106" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D106" s="4">
+        <v>1</v>
+      </c>
+      <c r="E106" s="4">
+        <v>1</v>
+      </c>
+      <c r="F106" s="4">
+        <v>1</v>
+      </c>
+      <c r="G106" s="2" t="s">
         <v>309</v>
       </c>
-      <c r="C105" s="1" t="s">
-        <v>296</v>
-      </c>
-      <c r="D105" s="4">
-        <v>1</v>
-      </c>
-      <c r="E105" s="4">
-        <v>1</v>
-      </c>
-      <c r="F105" s="4">
-        <v>1</v>
-      </c>
-      <c r="I105" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="106" spans="1:9" ht="54">
-      <c r="A106" s="4" t="s">
+      <c r="H106" s="2" t="s">
         <v>310</v>
       </c>
-      <c r="C106" s="1" t="s">
+      <c r="I106" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="107" spans="1:9" ht="67.5">
+      <c r="A107" s="4" t="s">
         <v>297</v>
       </c>
-      <c r="D106" s="4">
-        <v>1</v>
-      </c>
-      <c r="E106" s="4">
-        <v>1</v>
-      </c>
-      <c r="F106" s="4">
-        <v>1</v>
-      </c>
-      <c r="I106" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="107" spans="1:9" ht="54">
-      <c r="A107" s="4" t="s">
+      <c r="C107" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D107" s="4">
+        <v>1</v>
+      </c>
+      <c r="E107" s="4">
+        <v>1</v>
+      </c>
+      <c r="F107" s="4">
+        <v>1</v>
+      </c>
+      <c r="G107" s="2" t="s">
         <v>311</v>
       </c>
-      <c r="C107" s="1" t="s">
+      <c r="H107" s="2" t="s">
+        <v>312</v>
+      </c>
+      <c r="I107" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="108" spans="1:9" ht="67.5">
+      <c r="A108" s="4" t="s">
         <v>298</v>
       </c>
-      <c r="D107" s="4">
-        <v>1</v>
-      </c>
-      <c r="E107" s="4">
-        <v>1</v>
-      </c>
-      <c r="F107" s="4">
-        <v>1</v>
-      </c>
-      <c r="I107" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="108" spans="1:9" ht="54">
-      <c r="A108" s="4" t="s">
-        <v>312</v>
-      </c>
       <c r="C108" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D108" s="4">
+        <v>1</v>
+      </c>
+      <c r="E108" s="4">
+        <v>1</v>
+      </c>
+      <c r="F108" s="4">
+        <v>1</v>
+      </c>
+      <c r="G108" s="2" t="s">
+        <v>313</v>
+      </c>
+      <c r="H108" s="2" t="s">
+        <v>314</v>
+      </c>
+      <c r="I108" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="109" spans="1:9" ht="67.5">
+      <c r="A109" s="4" t="s">
         <v>299</v>
       </c>
-      <c r="D108" s="4">
-        <v>1</v>
-      </c>
-      <c r="E108" s="4">
-        <v>1</v>
-      </c>
-      <c r="F108" s="4">
-        <v>1</v>
-      </c>
-      <c r="I108" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="109" spans="1:9" ht="54">
-      <c r="A109" s="4" t="s">
-        <v>313</v>
-      </c>
       <c r="C109" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D109" s="4">
+        <v>1</v>
+      </c>
+      <c r="E109" s="4">
+        <v>1</v>
+      </c>
+      <c r="F109" s="4">
+        <v>1</v>
+      </c>
+      <c r="G109" s="2" t="s">
+        <v>315</v>
+      </c>
+      <c r="H109" s="2" t="s">
+        <v>316</v>
+      </c>
+      <c r="I109" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="110" spans="1:9" ht="67.5">
+      <c r="A110" s="4" t="s">
         <v>300</v>
       </c>
-      <c r="D109" s="4">
-        <v>1</v>
-      </c>
-      <c r="E109" s="4">
-        <v>1</v>
-      </c>
-      <c r="F109" s="4">
-        <v>1</v>
-      </c>
-      <c r="I109" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="110" spans="1:9" ht="67.5">
-      <c r="A110" s="2" t="s">
-        <v>314</v>
-      </c>
       <c r="C110" s="1" t="s">
         <v>22</v>
       </c>
@@ -4810,50 +5227,50 @@
         <v>1</v>
       </c>
       <c r="E110" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F110" s="4">
         <v>1</v>
       </c>
       <c r="G110" s="2" t="s">
+        <v>317</v>
+      </c>
+      <c r="H110" s="2" t="s">
         <v>316</v>
       </c>
-      <c r="H110" s="2" t="s">
+      <c r="I110" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="111" spans="1:9" ht="67.5">
+      <c r="A111" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="C111" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D111" s="4">
+        <v>1</v>
+      </c>
+      <c r="E111" s="4">
+        <v>2</v>
+      </c>
+      <c r="F111" s="4">
+        <v>1</v>
+      </c>
+      <c r="G111" s="2" t="s">
+        <v>318</v>
+      </c>
+      <c r="H111" s="2" t="s">
         <v>254</v>
       </c>
-      <c r="I110" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="111" spans="1:9" ht="54">
-      <c r="A111" s="2" t="s">
-        <v>315</v>
-      </c>
-      <c r="C111" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="D111" s="4">
-        <v>1</v>
-      </c>
-      <c r="E111" s="4">
-        <v>2</v>
-      </c>
-      <c r="F111" s="4">
-        <v>1</v>
-      </c>
-      <c r="G111" s="2" t="s">
-        <v>317</v>
-      </c>
-      <c r="H111" s="2" t="s">
-        <v>46</v>
-      </c>
       <c r="I111" s="4">
         <v>1</v>
       </c>
     </row>
-    <row r="112" spans="1:9" ht="67.5">
+    <row r="112" spans="1:9" ht="54">
       <c r="A112" s="2" t="s">
-        <v>318</v>
+        <v>302</v>
       </c>
       <c r="C112" s="1" t="s">
         <v>22</v>
@@ -4862,7 +5279,7 @@
         <v>1</v>
       </c>
       <c r="E112" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F112" s="4">
         <v>1</v>
@@ -4871,15 +5288,18 @@
         <v>319</v>
       </c>
       <c r="H112" s="2" t="s">
-        <v>277</v>
+        <v>46</v>
       </c>
       <c r="I112" s="4">
         <v>1</v>
       </c>
     </row>
-    <row r="113" spans="3:9" ht="54">
+    <row r="113" spans="1:9" ht="67.5">
+      <c r="A113" s="2" t="s">
+        <v>303</v>
+      </c>
       <c r="C113" s="1" t="s">
-        <v>301</v>
+        <v>22</v>
       </c>
       <c r="D113" s="4">
         <v>1</v>
@@ -4890,13 +5310,25 @@
       <c r="F113" s="4">
         <v>1</v>
       </c>
+      <c r="G113" s="2" t="s">
+        <v>320</v>
+      </c>
+      <c r="H113" s="2" t="s">
+        <v>321</v>
+      </c>
       <c r="I113" s="4">
         <v>1</v>
       </c>
     </row>
-    <row r="114" spans="3:9" ht="54">
+    <row r="114" spans="1:9" ht="94.5">
+      <c r="A114" s="4" t="s">
+        <v>346</v>
+      </c>
+      <c r="B114" s="6" t="s">
+        <v>322</v>
+      </c>
       <c r="C114" s="1" t="s">
-        <v>302</v>
+        <v>22</v>
       </c>
       <c r="D114" s="4">
         <v>1</v>
@@ -4907,13 +5339,22 @@
       <c r="F114" s="4">
         <v>1</v>
       </c>
+      <c r="G114" s="2" t="s">
+        <v>330</v>
+      </c>
+      <c r="H114" s="2" t="s">
+        <v>331</v>
+      </c>
       <c r="I114" s="4">
         <v>1</v>
       </c>
     </row>
-    <row r="115" spans="3:9" ht="54">
+    <row r="115" spans="1:9" ht="67.5">
+      <c r="A115" s="4" t="s">
+        <v>332</v>
+      </c>
       <c r="C115" s="1" t="s">
-        <v>303</v>
+        <v>22</v>
       </c>
       <c r="D115" s="4">
         <v>1</v>
@@ -4924,13 +5365,22 @@
       <c r="F115" s="4">
         <v>1</v>
       </c>
+      <c r="G115" s="2" t="s">
+        <v>333</v>
+      </c>
+      <c r="H115" s="2" t="s">
+        <v>334</v>
+      </c>
       <c r="I115" s="4">
         <v>1</v>
       </c>
     </row>
-    <row r="116" spans="3:9" ht="54">
+    <row r="116" spans="1:9" ht="67.5">
+      <c r="A116" s="4" t="s">
+        <v>335</v>
+      </c>
       <c r="C116" s="1" t="s">
-        <v>304</v>
+        <v>22</v>
       </c>
       <c r="D116" s="4">
         <v>1</v>
@@ -4941,13 +5391,22 @@
       <c r="F116" s="4">
         <v>1</v>
       </c>
+      <c r="G116" s="2" t="s">
+        <v>336</v>
+      </c>
+      <c r="H116" s="2" t="s">
+        <v>337</v>
+      </c>
       <c r="I116" s="4">
         <v>1</v>
       </c>
     </row>
-    <row r="117" spans="3:9" ht="54">
+    <row r="117" spans="1:9" ht="67.5">
+      <c r="A117" s="4" t="s">
+        <v>323</v>
+      </c>
       <c r="C117" s="1" t="s">
-        <v>305</v>
+        <v>22</v>
       </c>
       <c r="D117" s="4">
         <v>1</v>
@@ -4958,13 +5417,22 @@
       <c r="F117" s="4">
         <v>1</v>
       </c>
+      <c r="G117" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="H117" s="2" t="s">
+        <v>312</v>
+      </c>
       <c r="I117" s="4">
         <v>1</v>
       </c>
     </row>
-    <row r="118" spans="3:9" ht="54">
+    <row r="118" spans="1:9" ht="67.5">
+      <c r="A118" s="4" t="s">
+        <v>324</v>
+      </c>
       <c r="C118" s="1" t="s">
-        <v>306</v>
+        <v>22</v>
       </c>
       <c r="D118" s="4">
         <v>1</v>
@@ -4975,13 +5443,22 @@
       <c r="F118" s="4">
         <v>1</v>
       </c>
+      <c r="G118" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="H118" s="2" t="s">
+        <v>314</v>
+      </c>
       <c r="I118" s="4">
         <v>1</v>
       </c>
     </row>
-    <row r="119" spans="3:9" ht="54">
+    <row r="119" spans="1:9" ht="67.5">
+      <c r="A119" s="4" t="s">
+        <v>325</v>
+      </c>
       <c r="C119" s="1" t="s">
-        <v>307</v>
+        <v>22</v>
       </c>
       <c r="D119" s="4">
         <v>1</v>
@@ -4992,7 +5469,1069 @@
       <c r="F119" s="4">
         <v>1</v>
       </c>
+      <c r="G119" s="2" t="s">
+        <v>340</v>
+      </c>
+      <c r="H119" s="2" t="s">
+        <v>316</v>
+      </c>
       <c r="I119" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="120" spans="1:9" ht="67.5">
+      <c r="A120" s="4" t="s">
+        <v>326</v>
+      </c>
+      <c r="C120" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D120" s="4">
+        <v>1</v>
+      </c>
+      <c r="E120" s="4">
+        <v>1</v>
+      </c>
+      <c r="F120" s="4">
+        <v>1</v>
+      </c>
+      <c r="G120" s="2" t="s">
+        <v>341</v>
+      </c>
+      <c r="H120" s="2" t="s">
+        <v>316</v>
+      </c>
+      <c r="I120" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="121" spans="1:9" ht="67.5">
+      <c r="A121" s="2" t="s">
+        <v>327</v>
+      </c>
+      <c r="C121" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D121" s="4">
+        <v>1</v>
+      </c>
+      <c r="E121" s="4">
+        <v>2</v>
+      </c>
+      <c r="F121" s="4">
+        <v>1</v>
+      </c>
+      <c r="G121" s="2" t="s">
+        <v>342</v>
+      </c>
+      <c r="H121" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="I121" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="122" spans="1:9" ht="54">
+      <c r="A122" s="2" t="s">
+        <v>328</v>
+      </c>
+      <c r="C122" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D122" s="4">
+        <v>1</v>
+      </c>
+      <c r="E122" s="4">
+        <v>2</v>
+      </c>
+      <c r="F122" s="4">
+        <v>1</v>
+      </c>
+      <c r="G122" s="2" t="s">
+        <v>343</v>
+      </c>
+      <c r="H122" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="I122" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="123" spans="1:9" ht="67.5">
+      <c r="A123" s="2" t="s">
+        <v>329</v>
+      </c>
+      <c r="C123" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D123" s="4">
+        <v>1</v>
+      </c>
+      <c r="E123" s="4">
+        <v>1</v>
+      </c>
+      <c r="F123" s="4">
+        <v>1</v>
+      </c>
+      <c r="G123" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="H123" s="2" t="s">
+        <v>345</v>
+      </c>
+      <c r="I123" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="124" spans="1:9" ht="94.5">
+      <c r="A124" s="4" t="s">
+        <v>352</v>
+      </c>
+      <c r="B124" s="6" t="s">
+        <v>351</v>
+      </c>
+      <c r="C124" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D124" s="4">
+        <v>1</v>
+      </c>
+      <c r="E124" s="4">
+        <v>1</v>
+      </c>
+      <c r="F124" s="4">
+        <v>1</v>
+      </c>
+      <c r="G124" s="2" t="s">
+        <v>353</v>
+      </c>
+      <c r="H124" s="2" t="s">
+        <v>347</v>
+      </c>
+      <c r="I124" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="125" spans="1:9" ht="67.5">
+      <c r="A125" s="4" t="s">
+        <v>354</v>
+      </c>
+      <c r="C125" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D125" s="4">
+        <v>1</v>
+      </c>
+      <c r="E125" s="4">
+        <v>1</v>
+      </c>
+      <c r="F125" s="4">
+        <v>1</v>
+      </c>
+      <c r="G125" s="2" t="s">
+        <v>355</v>
+      </c>
+      <c r="H125" s="2" t="s">
+        <v>348</v>
+      </c>
+      <c r="I125" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="126" spans="1:9" ht="67.5">
+      <c r="A126" s="4" t="s">
+        <v>356</v>
+      </c>
+      <c r="C126" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D126" s="4">
+        <v>1</v>
+      </c>
+      <c r="E126" s="4">
+        <v>1</v>
+      </c>
+      <c r="F126" s="4">
+        <v>1</v>
+      </c>
+      <c r="G126" s="2" t="s">
+        <v>357</v>
+      </c>
+      <c r="H126" s="2" t="s">
+        <v>349</v>
+      </c>
+      <c r="I126" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="127" spans="1:9" ht="67.5">
+      <c r="A127" s="4" t="s">
+        <v>358</v>
+      </c>
+      <c r="C127" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D127" s="4">
+        <v>1</v>
+      </c>
+      <c r="E127" s="4">
+        <v>1</v>
+      </c>
+      <c r="F127" s="4">
+        <v>1</v>
+      </c>
+      <c r="G127" s="2" t="s">
+        <v>359</v>
+      </c>
+      <c r="H127" s="2" t="s">
+        <v>312</v>
+      </c>
+      <c r="I127" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="128" spans="1:9" ht="67.5">
+      <c r="A128" s="4" t="s">
+        <v>360</v>
+      </c>
+      <c r="C128" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D128" s="4">
+        <v>1</v>
+      </c>
+      <c r="E128" s="4">
+        <v>1</v>
+      </c>
+      <c r="F128" s="4">
+        <v>1</v>
+      </c>
+      <c r="G128" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="H128" s="2" t="s">
+        <v>314</v>
+      </c>
+      <c r="I128" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="129" spans="1:9" ht="67.5">
+      <c r="A129" s="4" t="s">
+        <v>362</v>
+      </c>
+      <c r="C129" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D129" s="4">
+        <v>1</v>
+      </c>
+      <c r="E129" s="4">
+        <v>1</v>
+      </c>
+      <c r="F129" s="4">
+        <v>1</v>
+      </c>
+      <c r="G129" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="H129" s="2" t="s">
+        <v>316</v>
+      </c>
+      <c r="I129" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="130" spans="1:9" ht="54">
+      <c r="A130" s="4" t="s">
+        <v>364</v>
+      </c>
+      <c r="C130" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D130" s="4">
+        <v>1</v>
+      </c>
+      <c r="E130" s="4">
+        <v>1</v>
+      </c>
+      <c r="F130" s="4">
+        <v>1</v>
+      </c>
+      <c r="G130" s="2" t="s">
+        <v>365</v>
+      </c>
+      <c r="H130" s="2" t="s">
+        <v>316</v>
+      </c>
+      <c r="I130" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="131" spans="1:9" ht="67.5">
+      <c r="A131" s="2" t="s">
+        <v>366</v>
+      </c>
+      <c r="C131" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D131" s="4">
+        <v>1</v>
+      </c>
+      <c r="E131" s="4">
+        <v>2</v>
+      </c>
+      <c r="F131" s="4">
+        <v>1</v>
+      </c>
+      <c r="G131" s="2" t="s">
+        <v>367</v>
+      </c>
+      <c r="H131" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="I131" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="132" spans="1:9" ht="54">
+      <c r="A132" s="2" t="s">
+        <v>368</v>
+      </c>
+      <c r="C132" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D132" s="4">
+        <v>1</v>
+      </c>
+      <c r="E132" s="4">
+        <v>2</v>
+      </c>
+      <c r="F132" s="4">
+        <v>1</v>
+      </c>
+      <c r="G132" s="2" t="s">
+        <v>369</v>
+      </c>
+      <c r="H132" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="I132" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="133" spans="1:9" ht="67.5">
+      <c r="A133" s="2" t="s">
+        <v>370</v>
+      </c>
+      <c r="C133" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D133" s="4">
+        <v>1</v>
+      </c>
+      <c r="E133" s="4">
+        <v>1</v>
+      </c>
+      <c r="F133" s="4">
+        <v>1</v>
+      </c>
+      <c r="G133" s="2" t="s">
+        <v>371</v>
+      </c>
+      <c r="H133" s="2" t="s">
+        <v>350</v>
+      </c>
+      <c r="I133" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="134" spans="1:9" ht="189">
+      <c r="A134" s="1" t="s">
+        <v>372</v>
+      </c>
+      <c r="B134" s="5" t="s">
+        <v>373</v>
+      </c>
+      <c r="C134" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D134" s="4">
+        <v>1</v>
+      </c>
+      <c r="E134" s="4">
+        <v>1</v>
+      </c>
+      <c r="F134" s="4">
+        <v>1</v>
+      </c>
+      <c r="I134" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="135" spans="1:9" ht="54">
+      <c r="A135" s="1" t="s">
+        <v>374</v>
+      </c>
+      <c r="B135" s="5" t="s">
+        <v>376</v>
+      </c>
+      <c r="C135" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D135" s="4">
+        <v>1</v>
+      </c>
+      <c r="E135" s="4">
+        <v>1</v>
+      </c>
+      <c r="F135" s="4">
+        <v>1</v>
+      </c>
+      <c r="I135" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="136" spans="1:9" ht="54">
+      <c r="A136" s="1" t="s">
+        <v>375</v>
+      </c>
+      <c r="B136" s="5" t="s">
+        <v>377</v>
+      </c>
+      <c r="C136" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D136" s="4">
+        <v>1</v>
+      </c>
+      <c r="E136" s="4">
+        <v>1</v>
+      </c>
+      <c r="F136" s="4">
+        <v>1</v>
+      </c>
+      <c r="I136" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="137" spans="1:9" ht="54">
+      <c r="A137" s="1" t="s">
+        <v>384</v>
+      </c>
+      <c r="B137" s="5" t="s">
+        <v>385</v>
+      </c>
+      <c r="C137" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D137" s="4">
+        <v>1</v>
+      </c>
+      <c r="E137" s="4">
+        <v>1</v>
+      </c>
+      <c r="F137" s="4">
+        <v>1</v>
+      </c>
+      <c r="I137" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="138" spans="1:9" ht="54">
+      <c r="A138" s="1" t="s">
+        <v>378</v>
+      </c>
+      <c r="B138" s="5" t="s">
+        <v>379</v>
+      </c>
+      <c r="C138" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D138" s="4">
+        <v>1</v>
+      </c>
+      <c r="E138" s="4">
+        <v>1</v>
+      </c>
+      <c r="F138" s="4">
+        <v>1</v>
+      </c>
+      <c r="I138" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="139" spans="1:9" ht="54">
+      <c r="A139" s="1" t="s">
+        <v>382</v>
+      </c>
+      <c r="B139" s="5" t="s">
+        <v>383</v>
+      </c>
+      <c r="C139" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D139" s="4">
+        <v>1</v>
+      </c>
+      <c r="E139" s="4">
+        <v>1</v>
+      </c>
+      <c r="F139" s="4">
+        <v>1</v>
+      </c>
+      <c r="I139" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="140" spans="1:9" ht="54">
+      <c r="A140" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="B140" s="5" t="s">
+        <v>381</v>
+      </c>
+      <c r="C140" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D140" s="4">
+        <v>1</v>
+      </c>
+      <c r="E140" s="4">
+        <v>1</v>
+      </c>
+      <c r="F140" s="4">
+        <v>1</v>
+      </c>
+      <c r="I140" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="141" spans="1:9" ht="54">
+      <c r="A141" s="1" t="s">
+        <v>387</v>
+      </c>
+      <c r="B141" s="5" t="s">
+        <v>389</v>
+      </c>
+      <c r="C141" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D141" s="4">
+        <v>1</v>
+      </c>
+      <c r="E141" s="4">
+        <v>1</v>
+      </c>
+      <c r="F141" s="4">
+        <v>1</v>
+      </c>
+      <c r="I141" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="142" spans="1:9" ht="54">
+      <c r="A142" s="1" t="s">
+        <v>386</v>
+      </c>
+      <c r="B142" s="5" t="s">
+        <v>388</v>
+      </c>
+      <c r="C142" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D142" s="4">
+        <v>1</v>
+      </c>
+      <c r="E142" s="4">
+        <v>1</v>
+      </c>
+      <c r="F142" s="4">
+        <v>1</v>
+      </c>
+      <c r="I142" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="143" spans="1:9" ht="54">
+      <c r="A143" s="1" t="s">
+        <v>391</v>
+      </c>
+      <c r="B143" s="5" t="s">
+        <v>392</v>
+      </c>
+      <c r="C143" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D143" s="4">
+        <v>1</v>
+      </c>
+      <c r="E143" s="4">
+        <v>1</v>
+      </c>
+      <c r="F143" s="4">
+        <v>1</v>
+      </c>
+      <c r="I143" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="144" spans="1:9" ht="54">
+      <c r="A144" s="1" t="s">
+        <v>390</v>
+      </c>
+      <c r="B144" s="5" t="s">
+        <v>393</v>
+      </c>
+      <c r="C144" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D144" s="4">
+        <v>1</v>
+      </c>
+      <c r="E144" s="4">
+        <v>1</v>
+      </c>
+      <c r="F144" s="4">
+        <v>1</v>
+      </c>
+      <c r="I144" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="145" spans="1:9" ht="54">
+      <c r="A145" s="1" t="s">
+        <v>394</v>
+      </c>
+      <c r="B145" s="5" t="s">
+        <v>396</v>
+      </c>
+      <c r="C145" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D145" s="4">
+        <v>1</v>
+      </c>
+      <c r="E145" s="4">
+        <v>1</v>
+      </c>
+      <c r="F145" s="4">
+        <v>1</v>
+      </c>
+      <c r="I145" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="146" spans="1:9" ht="54">
+      <c r="A146" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="B146" s="5" t="s">
+        <v>397</v>
+      </c>
+      <c r="C146" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D146" s="4">
+        <v>1</v>
+      </c>
+      <c r="E146" s="4">
+        <v>1</v>
+      </c>
+      <c r="F146" s="4">
+        <v>1</v>
+      </c>
+      <c r="I146" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="147" spans="1:9" ht="54">
+      <c r="A147" s="1" t="s">
+        <v>398</v>
+      </c>
+      <c r="B147" s="5" t="s">
+        <v>399</v>
+      </c>
+      <c r="C147" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D147" s="4">
+        <v>1</v>
+      </c>
+      <c r="E147" s="4">
+        <v>1</v>
+      </c>
+      <c r="F147" s="4">
+        <v>1</v>
+      </c>
+      <c r="I147" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="148" spans="1:9" ht="54">
+      <c r="A148" s="1" t="s">
+        <v>400</v>
+      </c>
+      <c r="B148" s="5" t="s">
+        <v>404</v>
+      </c>
+      <c r="C148" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D148" s="4">
+        <v>1</v>
+      </c>
+      <c r="E148" s="4">
+        <v>1</v>
+      </c>
+      <c r="F148" s="4">
+        <v>1</v>
+      </c>
+      <c r="I148" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="149" spans="1:9" ht="54">
+      <c r="A149" s="1" t="s">
+        <v>401</v>
+      </c>
+      <c r="B149" s="5" t="s">
+        <v>405</v>
+      </c>
+      <c r="C149" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D149" s="4">
+        <v>1</v>
+      </c>
+      <c r="E149" s="4">
+        <v>1</v>
+      </c>
+      <c r="F149" s="4">
+        <v>1</v>
+      </c>
+      <c r="I149" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="150" spans="1:9" ht="54">
+      <c r="A150" s="1" t="s">
+        <v>402</v>
+      </c>
+      <c r="B150" s="5" t="s">
+        <v>406</v>
+      </c>
+      <c r="C150" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D150" s="4">
+        <v>1</v>
+      </c>
+      <c r="E150" s="4">
+        <v>1</v>
+      </c>
+      <c r="F150" s="4">
+        <v>1</v>
+      </c>
+      <c r="I150" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="151" spans="1:9" ht="54">
+      <c r="A151" s="1" t="s">
+        <v>403</v>
+      </c>
+      <c r="B151" s="5" t="s">
+        <v>407</v>
+      </c>
+      <c r="C151" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D151" s="4">
+        <v>1</v>
+      </c>
+      <c r="E151" s="4">
+        <v>1</v>
+      </c>
+      <c r="F151" s="4">
+        <v>1</v>
+      </c>
+      <c r="I151" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="152" spans="1:9" ht="54">
+      <c r="A152" s="1" t="s">
+        <v>410</v>
+      </c>
+      <c r="B152" s="5" t="s">
+        <v>411</v>
+      </c>
+      <c r="C152" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D152" s="4">
+        <v>1</v>
+      </c>
+      <c r="E152" s="4">
+        <v>1</v>
+      </c>
+      <c r="F152" s="4">
+        <v>1</v>
+      </c>
+      <c r="I152" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="153" spans="1:9" ht="54">
+      <c r="A153" s="1" t="s">
+        <v>408</v>
+      </c>
+      <c r="B153" s="5" t="s">
+        <v>409</v>
+      </c>
+      <c r="C153" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D153" s="4">
+        <v>1</v>
+      </c>
+      <c r="E153" s="4">
+        <v>1</v>
+      </c>
+      <c r="F153" s="4">
+        <v>1</v>
+      </c>
+      <c r="I153" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="154" spans="1:9" ht="67.5">
+      <c r="A154" s="1" t="s">
+        <v>412</v>
+      </c>
+      <c r="B154" s="5" t="s">
+        <v>413</v>
+      </c>
+      <c r="C154" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D154" s="4">
+        <v>1</v>
+      </c>
+      <c r="E154" s="4">
+        <v>1</v>
+      </c>
+      <c r="F154" s="4">
+        <v>1</v>
+      </c>
+      <c r="I154" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="155" spans="1:9" ht="54">
+      <c r="A155" s="1" t="s">
+        <v>416</v>
+      </c>
+      <c r="B155" s="5" t="s">
+        <v>417</v>
+      </c>
+      <c r="C155" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D155" s="4">
+        <v>1</v>
+      </c>
+      <c r="E155" s="4">
+        <v>1</v>
+      </c>
+      <c r="F155" s="4">
+        <v>1</v>
+      </c>
+      <c r="I155" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="156" spans="1:9" ht="54">
+      <c r="A156" s="1" t="s">
+        <v>422</v>
+      </c>
+      <c r="B156" s="5" t="s">
+        <v>417</v>
+      </c>
+      <c r="C156" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D156" s="4">
+        <v>1</v>
+      </c>
+      <c r="E156" s="4">
+        <v>1</v>
+      </c>
+      <c r="F156" s="4">
+        <v>1</v>
+      </c>
+      <c r="I156" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="157" spans="1:9" ht="54">
+      <c r="A157" s="1" t="s">
+        <v>415</v>
+      </c>
+      <c r="C157" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D157" s="4">
+        <v>1</v>
+      </c>
+      <c r="E157" s="4">
+        <v>1</v>
+      </c>
+      <c r="F157" s="4">
+        <v>1</v>
+      </c>
+      <c r="I157" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="158" spans="1:9" ht="54">
+      <c r="A158" s="1" t="s">
+        <v>414</v>
+      </c>
+      <c r="C158" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D158" s="4">
+        <v>1</v>
+      </c>
+      <c r="E158" s="4">
+        <v>1</v>
+      </c>
+      <c r="F158" s="4">
+        <v>1</v>
+      </c>
+      <c r="I158" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="159" spans="1:9" ht="54">
+      <c r="A159" s="1" t="s">
+        <v>414</v>
+      </c>
+      <c r="C159" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D159" s="4">
+        <v>1</v>
+      </c>
+      <c r="E159" s="4">
+        <v>1</v>
+      </c>
+      <c r="F159" s="4">
+        <v>1</v>
+      </c>
+      <c r="I159" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="160" spans="1:9" ht="54">
+      <c r="A160" s="1" t="s">
+        <v>418</v>
+      </c>
+      <c r="C160" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D160" s="4">
+        <v>1</v>
+      </c>
+      <c r="E160" s="4">
+        <v>1</v>
+      </c>
+      <c r="F160" s="4">
+        <v>1</v>
+      </c>
+      <c r="I160" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="161" spans="1:9" ht="54">
+      <c r="A161" s="1" t="s">
+        <v>419</v>
+      </c>
+      <c r="C161" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D161" s="4">
+        <v>1</v>
+      </c>
+      <c r="E161" s="4">
+        <v>1</v>
+      </c>
+      <c r="F161" s="4">
+        <v>1</v>
+      </c>
+      <c r="I161" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="162" spans="1:9" ht="54">
+      <c r="A162" s="1" t="s">
+        <v>420</v>
+      </c>
+      <c r="C162" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D162" s="4">
+        <v>1</v>
+      </c>
+      <c r="E162" s="4">
+        <v>1</v>
+      </c>
+      <c r="F162" s="4">
+        <v>1</v>
+      </c>
+      <c r="I162" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="163" spans="1:9" ht="54">
+      <c r="A163" s="1" t="s">
+        <v>421</v>
+      </c>
+      <c r="C163" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D163" s="4">
+        <v>1</v>
+      </c>
+      <c r="E163" s="4">
+        <v>1</v>
+      </c>
+      <c r="F163" s="4">
+        <v>1</v>
+      </c>
+      <c r="I163" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="164" spans="1:9" ht="54">
+      <c r="A164" s="1" t="s">
+        <v>423</v>
+      </c>
+      <c r="C164" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D164" s="4">
+        <v>1</v>
+      </c>
+      <c r="E164" s="4">
+        <v>1</v>
+      </c>
+      <c r="F164" s="4">
+        <v>1</v>
+      </c>
+      <c r="I164" s="4">
         <v>1</v>
       </c>
     </row>
